--- a/db/A7XLK-2205-Election.xlsx
+++ b/db/A7XLK-2205-Election.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10520"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A2DA40-B532-3948-8BDC-015E6A193BDB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E305A3-3AF4-C94F-A16F-9B9255457BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-300" yWindow="-17320" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-3920" yWindow="-13600" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="39">
   <si>
     <t>no</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -173,6 +173,22 @@
   </si>
   <si>
     <t>https://zh.wikipedia.org/wiki/%E6%9E%97%E6%99%BA%E5%A0%85</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ig</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/hsianglinlai/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/sancheng624/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://www.instagram.com/lin_chihchien/</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -553,7 +569,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A569E7E5-CF2A-7E44-B2C2-91A32E7499FF}">
-  <dimension ref="A1:L4"/>
+  <dimension ref="A1:M4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="5.83203125" customWidth="1"/>
@@ -563,11 +579,11 @@
     <col min="7" max="8" width="19.5" customWidth="1"/>
     <col min="9" max="9" width="30.1640625" customWidth="1"/>
     <col min="10" max="10" width="26.6640625" customWidth="1"/>
-    <col min="11" max="11" width="56" customWidth="1"/>
-    <col min="12" max="12" width="50.6640625" customWidth="1"/>
+    <col min="11" max="12" width="56" customWidth="1"/>
+    <col min="13" max="13" width="50.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12">
+    <row r="1" spans="1:13">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -602,10 +618,13 @@
         <v>7</v>
       </c>
       <c r="L1" t="s">
+        <v>35</v>
+      </c>
+      <c r="M1" t="s">
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:12">
+    <row r="2" spans="1:13">
       <c r="A2">
         <v>101</v>
       </c>
@@ -631,11 +650,14 @@
       <c r="K2" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
+        <v>38</v>
+      </c>
+      <c r="M2" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:12">
+    <row r="3" spans="1:13">
       <c r="A3">
         <v>102</v>
       </c>
@@ -661,11 +683,14 @@
       <c r="K3" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
+        <v>37</v>
+      </c>
+      <c r="M3" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:12">
+    <row r="4" spans="1:13">
       <c r="A4">
         <v>103</v>
       </c>
@@ -693,12 +718,15 @@
       <c r="K4" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="M4" t="s">
         <v>30</v>
       </c>
     </row>
   </sheetData>
-  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:L4">
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:M4">
     <sortCondition ref="A2:A4"/>
   </sortState>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -713,6 +741,9 @@
     <hyperlink ref="H4" r:id="rId8" xr:uid="{09214374-1FED-5D46-997C-56641F730EFB}"/>
     <hyperlink ref="H3" r:id="rId9" xr:uid="{B888F716-0516-CC40-A013-01F99C493C5B}"/>
     <hyperlink ref="H2" r:id="rId10" xr:uid="{B4C5F3C9-4A60-8D45-BCAD-67D6DC1B42E1}"/>
+    <hyperlink ref="L4" r:id="rId11" xr:uid="{36D2592E-4E0A-424E-A9B9-894E5FC848F3}"/>
+    <hyperlink ref="L3" r:id="rId12" xr:uid="{A67B2FC9-18A8-F843-B449-A31ADC8D6D13}"/>
+    <hyperlink ref="L2" r:id="rId13" xr:uid="{F52880C5-38B8-8543-BABE-A91E15479ABF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/db/A7XLK-2205-Election.xlsx
+++ b/db/A7XLK-2205-Election.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{52E305A3-3AF4-C94F-A16F-9B9255457BF6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098EE65A-EEED-A746-9E41-B5AD0581D4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3920" yWindow="-13600" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-5200" yWindow="-17700" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -152,10 +152,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>前行政院長,  &lt;a href="https://line.me/R/ti/p/@who9307k"&gt;Line 群組 &lt;/a&gt;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>現任 立法委員 &lt;a href="https://2022.tycwin.app/%E5%85%B1%E6%8F%90%E6%94%BF%E8%A6%8B"&gt;共提政見網頁&lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -189,6 +185,10 @@
   </si>
   <si>
     <t>https://www.instagram.com/lin_chihchien/</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>前行政院長,  &lt;a href="https://line.me/R/ti/p/@who9307k"&gt;Line 張善政 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/UJULFO1xB4jiLXTHG2HZygIOkokfFHX-ulFWqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 桃園後援會 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/WjGLPNbMe8QCTenSqiZdZ8ZM-t4jvT0YH1JIqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 全國後援會 &lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -606,7 +606,7 @@
         <v>5</v>
       </c>
       <c r="H1" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="I1" t="s">
         <v>6</v>
@@ -618,7 +618,7 @@
         <v>7</v>
       </c>
       <c r="L1" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="M1" t="s">
         <v>9</v>
@@ -639,7 +639,7 @@
       </c>
       <c r="G2" s="1"/>
       <c r="H2" s="1" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>27</v>
@@ -651,7 +651,7 @@
         <v>21</v>
       </c>
       <c r="L2" s="1" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="M2" t="s">
         <v>28</v>
@@ -672,7 +672,7 @@
       </c>
       <c r="G3" s="1"/>
       <c r="H3" s="1" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="I3" s="1" t="s">
         <v>26</v>
@@ -684,10 +684,10 @@
         <v>22</v>
       </c>
       <c r="L3" s="1" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="M3" t="s">
-        <v>29</v>
+        <v>38</v>
       </c>
     </row>
     <row r="4" spans="1:13">
@@ -707,7 +707,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="1" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="I4" s="1" t="s">
         <v>24</v>
@@ -719,10 +719,10 @@
         <v>23</v>
       </c>
       <c r="L4" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="M4" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
     </row>
   </sheetData>

--- a/db/A7XLK-2205-Election.xlsx
+++ b/db/A7XLK-2205-Election.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{098EE65A-EEED-A746-9E41-B5AD0581D4F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9BAD64-AB9B-CA4D-A7E9-529AA91F86AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-5200" yWindow="-17700" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="-3540" yWindow="-17140" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -188,7 +188,7 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>前行政院長,  &lt;a href="https://line.me/R/ti/p/@who9307k"&gt;Line 張善政 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/UJULFO1xB4jiLXTHG2HZygIOkokfFHX-ulFWqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 桃園後援會 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/WjGLPNbMe8QCTenSqiZdZ8ZM-t4jvT0YH1JIqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 全國後援會 &lt;/a&gt;</t>
+    <t>前行政院長,  &lt;a href="https://line.me/R/ti/p/@who9307k"&gt;Line 張善政 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/UJULFO1xB4jiLXTHG2HZygIOkokfFHX-ulFWqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 桃園後援會 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/WjGLPNbMe8QCTenSqiZdZ8ZM-t4jvT0YH1JIqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 全國後援會 &lt;/a&gt;,   &lt;a href="https://www.facebook.com/sancode2019/"&gt;FB 善科教育基金會 &lt;/a&gt;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>

--- a/db/A7XLK-2205-Election.xlsx
+++ b/db/A7XLK-2205-Election.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10611"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10713"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/wangtaizhong/Documents/92_WebSite/A7Xinlinkou/db/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D9BAD64-AB9B-CA4D-A7E9-529AA91F86AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{03246FF2-BED9-9F4E-8A98-FE6BEA84F856}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-3540" yWindow="-17140" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
+    <workbookView xWindow="3040" yWindow="-14320" windowWidth="27920" windowHeight="17320" xr2:uid="{7829DD84-CEBD-774C-BB30-384CAE524C7F}"/>
   </bookViews>
   <sheets>
     <sheet name="工作表1" sheetId="1" r:id="rId1"/>
@@ -188,7 +188,8 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>前行政院長,  &lt;a href="https://line.me/R/ti/p/@who9307k"&gt;Line 張善政 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/UJULFO1xB4jiLXTHG2HZygIOkokfFHX-ulFWqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 桃園後援會 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/WjGLPNbMe8QCTenSqiZdZ8ZM-t4jvT0YH1JIqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 全國後援會 &lt;/a&gt;,   &lt;a href="https://www.facebook.com/sancode2019/"&gt;FB 善科教育基金會 &lt;/a&gt;</t>
+    <t>前行政院長,  &lt;a href="https://line.me/R/ti/p/@who9307k"&gt;Line 張善政 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/UJULFO1xB4jiLXTHG2HZygIOkokfFHX-ulFWqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 桃園後援會 &lt;/a&gt;,   &lt;a href="https://line.me/ti/g2/WjGLPNbMe8QCTenSqiZdZ8ZM-t4jvT0YH1JIqA?utm_source=invitation&amp;utm_medium=link_copy&amp;utm_campaign=default"&gt;Line 全國後援會 &lt;/a&gt;,   &lt;a href="https://www.facebook.com/sancode2019/"&gt;FB 善科教育基金會 &lt;/a&gt;, 
+&lt;a href="fig/XLK-221-Election/AiCity-2202-張善政-04.jpeg"&gt;張善政政治獻金專戶</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -247,12 +248,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -657,7 +661,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:13">
+    <row r="3" spans="1:13" ht="224">
       <c r="A3">
         <v>102</v>
       </c>
@@ -686,7 +690,7 @@
       <c r="L3" s="1" t="s">
         <v>36</v>
       </c>
-      <c r="M3" t="s">
+      <c r="M3" s="2" t="s">
         <v>38</v>
       </c>
     </row>
